--- a/grammatica_V2.0.xlsx
+++ b/grammatica_V2.0.xlsx
@@ -8,16 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\04_Wörterbücher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE5649B-15A4-4569-A73D-F2A4BFDB2F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9FB961-D1E6-4F74-9335-39E94960C0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="2" r:id="rId1"/>
     <sheet name="Präpositionen" sheetId="3" r:id="rId2"/>
+    <sheet name="Pronomi personali" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="112">
   <si>
     <t>it</t>
   </si>
@@ -501,6 +513,78 @@
       </rPr>
       <t>(da + le)</t>
     </r>
+  </si>
+  <si>
+    <t>io</t>
+  </si>
+  <si>
+    <t>mir</t>
+  </si>
+  <si>
+    <t>tu</t>
+  </si>
+  <si>
+    <t>dir</t>
+  </si>
+  <si>
+    <t>lui</t>
+  </si>
+  <si>
+    <t>ihm</t>
+  </si>
+  <si>
+    <t>lei</t>
+  </si>
+  <si>
+    <t>ihr</t>
+  </si>
+  <si>
+    <t>Lei (Höflichkeitsform)</t>
+  </si>
+  <si>
+    <t>Ihnen</t>
+  </si>
+  <si>
+    <t>noi</t>
+  </si>
+  <si>
+    <t>uns</t>
+  </si>
+  <si>
+    <t>voi</t>
+  </si>
+  <si>
+    <t>euch</t>
+  </si>
+  <si>
+    <t>loro</t>
+  </si>
+  <si>
+    <t>ihnen</t>
+  </si>
+  <si>
+    <t>io -&gt; mi</t>
+  </si>
+  <si>
+    <t>tu -&gt; ti</t>
+  </si>
+  <si>
+    <t>lui -&gt; gli</t>
+  </si>
+  <si>
+    <t>lei -&gt; le</t>
+  </si>
+  <si>
+    <t>Lei (Höflichkeitsform) -&gt; Le</t>
+  </si>
+  <si>
+    <t>noi -&gt; ci</t>
+  </si>
+  <si>
+    <t>voi -&gt; vi</t>
+  </si>
+  <si>
+    <t>loro -&gt; gli (loro)</t>
   </si>
 </sst>
 </file>
@@ -578,7 +662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -597,6 +681,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1320,4 +1407,135 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9670D57-2FB5-4673-BF1B-2FF36AA5D3C4}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/grammatica_V2.0.xlsx
+++ b/grammatica_V2.0.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\04_Wörterbücher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9FB961-D1E6-4F74-9335-39E94960C0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E0BEC2-FA30-43A6-A86B-9EDE201F192D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="2" r:id="rId1"/>
-    <sheet name="Präpositionen" sheetId="3" r:id="rId2"/>
-    <sheet name="Pronomi personali" sheetId="4" r:id="rId3"/>
+    <sheet name="Präpositionen" sheetId="5" r:id="rId2"/>
+    <sheet name="Präpositionen2" sheetId="3" r:id="rId3"/>
+    <sheet name="Pronomi personali" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="130">
   <si>
     <t>it</t>
   </si>
@@ -585,6 +586,235 @@
   </si>
   <si>
     <t>loro -&gt; gli (loro)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">a + il = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>al</t>
+    </r>
+  </si>
+  <si>
+    <t>zum / am</t>
+  </si>
+  <si>
+    <r>
+      <t>al museo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – zum Museum</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">a + lo = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>allo</t>
+    </r>
+  </si>
+  <si>
+    <t>zum</t>
+  </si>
+  <si>
+    <r>
+      <t>allo stadio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – zum Stadion</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">a + la = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>alla</t>
+    </r>
+  </si>
+  <si>
+    <t>zur / an der</t>
+  </si>
+  <si>
+    <r>
+      <t>alla banca</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – zur Bank</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">a + l' = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>all'</t>
+    </r>
+  </si>
+  <si>
+    <t>zum/zur</t>
+  </si>
+  <si>
+    <r>
+      <t>all'angolo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – an der Ecke</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">a + i = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>ai</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ai negozi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – zu den Geschäften</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">a + gli = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>agli</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>agli studenti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – zu den Schülern</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">a + le = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>alle</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>alle scuole</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> – zu den Schulen</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -662,7 +892,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -684,6 +914,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1107,27 +1340,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB60FFD2-C7FC-4157-AA6D-8FEC1F28793D}">
-  <dimension ref="A1:G21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B8F683-4B0B-4768-B927-697D835C9AA3}">
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="22.5546875" customWidth="1"/>
     <col min="4" max="4" width="45.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="22.5546875" customWidth="1"/>
+    <col min="11" max="11" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1149,8 +1383,11 @@
       <c r="G3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>74</v>
       </c>
@@ -1168,7 +1405,7 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>75</v>
       </c>
@@ -1185,8 +1422,11 @@
         <v>67</v>
       </c>
       <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>76</v>
       </c>
@@ -1202,8 +1442,11 @@
       <c r="F6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>77</v>
       </c>
@@ -1219,8 +1462,11 @@
       <c r="F7" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>78</v>
       </c>
@@ -1236,8 +1482,11 @@
       <c r="F8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>79</v>
       </c>
@@ -1254,8 +1503,11 @@
       <c r="F9" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>80</v>
       </c>
@@ -1272,8 +1524,11 @@
       <c r="F10" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>81</v>
       </c>
@@ -1290,8 +1545,11 @@
       <c r="F11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>82</v>
       </c>
@@ -1309,7 +1567,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>83</v>
       </c>
@@ -1326,7 +1584,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>84</v>
       </c>
@@ -1343,7 +1601,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>85</v>
       </c>
@@ -1360,7 +1618,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>86</v>
       </c>
@@ -1410,6 +1668,192 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB60FFD2-C7FC-4157-AA6D-8FEC1F28793D}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="22.5546875" customWidth="1"/>
+    <col min="4" max="4" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="22.5546875" customWidth="1"/>
+    <col min="11" max="11" width="29" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="C11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="8"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9670D57-2FB5-4673-BF1B-2FF36AA5D3C4}">
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
